--- a/data/trans_orig/P79_n_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R-Clase-trans_orig.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1025,12 +1025,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1167,32 +1167,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26936</t>
+          <t>32159</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39521</t>
+          <t>47108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1202,32 +1202,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>48955</t>
+          <t>58065</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37631</t>
+          <t>44576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>74919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>471356</t>
+          <t>509611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>457882</t>
+          <t>494238</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>480935</t>
+          <t>521284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1313,32 +1313,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>420422</t>
+          <t>456155</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>411352</t>
+          <t>444629</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>428277</t>
+          <t>465032</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1348,32 +1348,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>891778</t>
+          <t>965766</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>874616</t>
+          <t>946739</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>904195</t>
+          <t>980578</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1728,17 +1728,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,17 +1798,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1839,32 +1839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1874,32 +1874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1909,17 +1909,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>21364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1950,32 +1950,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33377</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>25599</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45841</t>
+          <t>51130</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1985,32 +1985,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39461</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29736</t>
+          <t>34395</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2020,32 +2020,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>72838</t>
+          <t>80928</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>65898</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>87902</t>
+          <t>97797</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -2061,32 +2061,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>410070</t>
+          <t>437378</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>395132</t>
+          <t>422345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>420164</t>
+          <t>449243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>336665</t>
+          <t>371585</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>324643</t>
+          <t>357578</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>347285</t>
+          <t>382532</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2131,32 +2131,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>746736</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>729289</t>
+          <t>790841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>761667</t>
+          <t>825721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2581,32 +2581,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2622,32 +2622,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42264</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2657,32 +2657,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2692,32 +2692,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>30069</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75230</t>
+          <t>63199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2768,32 +2768,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2803,32 +2803,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>67966</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>53829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>84511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -2844,32 +2844,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>599469</t>
+          <t>391794</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>550416</t>
+          <t>374498</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>643958</t>
+          <t>406361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2879,32 +2879,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>148683</t>
+          <t>165550</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>140982</t>
+          <t>157664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154148</t>
+          <t>172565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2914,32 +2914,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>748152</t>
+          <t>557344</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>706163</t>
+          <t>537847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>793942</t>
+          <t>575265</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -2957,17 +2957,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3027,17 +3027,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -3294,32 +3294,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3329,32 +3329,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3364,32 +3364,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3405,32 +3405,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>38091</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55363</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3440,32 +3440,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3475,32 +3475,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>54544</t>
+          <t>63751</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73015</t>
+          <t>81429</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3516,32 +3516,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>113104</t>
+          <t>129626</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>91311</t>
+          <t>106553</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>134784</t>
+          <t>156012</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3551,32 +3551,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>57518</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>57029</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>78129</t>
+          <t>84930</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3586,32 +3586,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>170622</t>
+          <t>199726</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>120566</t>
+          <t>175291</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>207151</t>
+          <t>234866</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -3627,32 +3627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>875733</t>
+          <t>949189</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>849577</t>
+          <t>919669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>901038</t>
+          <t>975262</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3662,32 +3662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>901172</t>
+          <t>769286</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>873638</t>
+          <t>752663</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>937766</t>
+          <t>783479</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3697,32 +3697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1776905</t>
+          <t>1718475</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1733310</t>
+          <t>1681744</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1847371</t>
+          <t>1749558</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -3740,17 +3740,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4001,32 +4001,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4036,32 +4036,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -4077,32 +4077,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4112,32 +4112,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4147,32 +4147,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4188,32 +4188,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>35030</t>
+          <t>39392</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4223,32 +4223,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>42674</t>
+          <t>53306</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>57184</t>
+          <t>67659</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4258,32 +4258,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>66254</t>
+          <t>80360</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>48607</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>84599</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -4299,32 +4299,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>55499</t>
+          <t>72170</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>43466</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>72613</t>
+          <t>92800</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4334,32 +4334,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>87709</t>
+          <t>98777</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>83649</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>107241</t>
+          <t>115486</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4369,32 +4369,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>143209</t>
+          <t>170947</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>117534</t>
+          <t>148626</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>167242</t>
+          <t>194760</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -4410,32 +4410,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>390319</t>
+          <t>462713</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>371909</t>
+          <t>441075</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>404429</t>
+          <t>480164</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4445,32 +4445,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>703957</t>
+          <t>669898</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>679266</t>
+          <t>649328</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>737354</t>
+          <t>689516</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4480,32 +4480,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1094276</t>
+          <t>1132611</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1064934</t>
+          <t>1103708</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1137608</t>
+          <t>1160089</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -4523,17 +4523,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4593,17 +4593,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -4784,22 +4784,22 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4819,22 +4819,22 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -4895,32 +4895,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>789</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4930,22 +4930,22 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4971,32 +4971,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5006,32 +5006,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>39685</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>44552</t>
+          <t>52772</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5041,32 +5041,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>63661</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -5082,32 +5082,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>85931</t>
+          <t>101081</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>70356</t>
+          <t>83419</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>103251</t>
+          <t>119149</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5152,32 +5152,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>96785</t>
+          <t>113528</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>79404</t>
+          <t>92878</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>118147</t>
+          <t>135881</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -5193,32 +5193,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>224672</t>
+          <t>217399</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>204599</t>
+          <t>199586</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>234587</t>
+          <t>227679</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5228,32 +5228,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>631532</t>
+          <t>696174</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>610636</t>
+          <t>672863</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>649956</t>
+          <t>715474</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5263,32 +5263,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>856203</t>
+          <t>913573</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>830184</t>
+          <t>886009</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>880034</t>
+          <t>937340</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -5306,17 +5306,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5376,17 +5376,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5532,22 +5532,22 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5567,17 +5567,17 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -5643,22 +5643,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>17448</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>29956</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>32403</t>
+          <t>26469</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5713,32 +5713,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>32511</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>48372</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -5754,32 +5754,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>101238</t>
+          <t>120201</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>77697</t>
+          <t>99411</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>126193</t>
+          <t>145314</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5789,32 +5789,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>107316</t>
+          <t>127409</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>85794</t>
+          <t>106953</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>128831</t>
+          <t>150034</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5824,32 +5824,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>208555</t>
+          <t>247610</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>175090</t>
+          <t>217744</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>241140</t>
+          <t>278658</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5865,32 +5865,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>282995</t>
+          <t>333211</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>222973</t>
+          <t>295073</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>324780</t>
+          <t>372003</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5900,32 +5900,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>307395</t>
+          <t>357949</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>255511</t>
+          <t>327608</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>345697</t>
+          <t>391702</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5935,32 +5935,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>590390</t>
+          <t>691160</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>506773</t>
+          <t>637992</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>647706</t>
+          <t>740940</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -5976,32 +5976,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2971618</t>
+          <t>2968082</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2919258</t>
+          <t>2922264</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3050934</t>
+          <t>3010494</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6011,32 +6011,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3142433</t>
+          <t>3128649</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3095395</t>
+          <t>3088226</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3219290</t>
+          <t>3167400</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6046,32 +6046,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>6114051</t>
+          <t>6096731</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>6037360</t>
+          <t>6042440</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>6223726</t>
+          <t>6162358</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>87,07%</t>
         </is>
       </c>
     </row>
@@ -6089,17 +6089,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
